--- a/02_Basic_Excel_for_Data_Analytics/20_Workbook-Reference-1.xlsx
+++ b/02_Basic_Excel_for_Data_Analytics/20_Workbook-Reference-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 COURSES\Learn_Data_Analytics_by_CWH\02_Basic_Excel_for_Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1628AD15-4B47-4CD5-BDC7-5C4CD58C5DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D96CB3-F236-4976-BD8F-7083C71C7EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -160,7 +160,7 @@
         </row>
         <row r="6">
           <cell r="B6">
-            <v>23</v>
+            <v>75</v>
           </cell>
         </row>
         <row r="7">
@@ -535,7 +535,7 @@
       </c>
       <c r="D7">
         <f>[1]Sheet1!$B6</f>
-        <v>23</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
